--- a/scripts/projects.xlsx
+++ b/scripts/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonatan/dev/WIP/portfolio-site/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70610FF5-6F00-3C44-B7B7-DF98C1CCB8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C5B3E5-D596-8E47-ABFC-553871D0E0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40460" yWindow="-3320" windowWidth="30240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40440" yWindow="320" windowWidth="30240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="253">
   <si>
     <t>id</t>
   </si>
@@ -541,9 +541,6 @@
     <t>chr2img</t>
   </si>
   <si>
-    <t>App (details pending)</t>
-  </si>
-  <si>
     <t>chr2img.webp</t>
   </si>
   <si>
@@ -761,6 +758,27 @@
   </si>
   <si>
     <t>peripage.webp</t>
+  </si>
+  <si>
+    <t>Game, retro</t>
+  </si>
+  <si>
+    <t>Tool, retro</t>
+  </si>
+  <si>
+    <t>CLI, Tool, retro</t>
+  </si>
+  <si>
+    <t>Tool, retro, CLI</t>
+  </si>
+  <si>
+    <t>GitHub|https://github.com/general-ackbar/img2nes</t>
+  </si>
+  <si>
+    <t>Creates a png screenshot from a NES character rom. Very simple</t>
+  </si>
+  <si>
+    <t>GitHub|https://github.com/general-ackbar/chr2img</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1281,7 @@
         <v>36</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>246</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -1341,7 +1359,7 @@
         <v>52</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
+        <v>246</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>12</v>
@@ -1367,7 +1385,7 @@
         <v>58</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>11</v>
+        <v>246</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>12</v>
@@ -1393,7 +1411,7 @@
         <v>64</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>11</v>
+        <v>246</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>12</v>
@@ -1419,7 +1437,7 @@
         <v>70</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>11</v>
+        <v>246</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>12</v>
@@ -1471,7 +1489,7 @@
         <v>82</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>11</v>
+        <v>246</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>12</v>
@@ -1729,7 +1747,7 @@
         <v>121</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>89</v>
+        <v>247</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>30</v>
@@ -1755,7 +1773,7 @@
         <v>121</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>89</v>
+        <v>247</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>30</v>
@@ -1793,7 +1811,7 @@
         <v>146</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -1819,7 +1837,7 @@
         <v>150</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="64" x14ac:dyDescent="0.2">
@@ -1833,7 +1851,7 @@
         <v>121</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>144</v>
+        <v>248</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>12</v>
@@ -1856,7 +1874,7 @@
         <v>156</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>144</v>
@@ -1879,7 +1897,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>121</v>
@@ -1891,13 +1909,13 @@
         <v>12</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -1911,7 +1929,7 @@
         <v>121</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>144</v>
+        <v>248</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
@@ -1960,182 +1978,184 @@
         <v>172</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="H33" s="2" t="s">
-        <v>44</v>
+        <v>252</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>89</v>
+        <v>249</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="G35" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="H35" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="G36" s="2" t="s">
+      <c r="H36" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="G37" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="H37" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="G38" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="H38" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C39" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F39" s="2" t="s">
+      <c r="G39" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="H39" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>121</v>
@@ -2144,10 +2164,10 @@
         <v>89</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2" t="s">
@@ -2156,10 +2176,10 @@
     </row>
     <row r="41" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>121</v>
@@ -2168,10 +2188,10 @@
         <v>89</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2" t="s">
@@ -2180,114 +2200,114 @@
     </row>
     <row r="42" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="E42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="G42" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="H42" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" s="2" t="s">
+      <c r="G43" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="H43" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="G44" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>121</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>144</v>
+        <v>249</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F45" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="H45" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>121</v>
@@ -2299,18 +2319,18 @@
         <v>12</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>121</v>
@@ -2322,13 +2342,13 @@
         <v>12</v>
       </c>
       <c r="F47" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="H47" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/projects.xlsx
+++ b/scripts/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonatan/dev/WIP/portfolio-site/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C5B3E5-D596-8E47-ABFC-553871D0E0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD560E3-C6E1-4843-AE88-A07137618947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40440" yWindow="320" windowWidth="30240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -751,9 +751,6 @@
     <t>peripagea6</t>
   </si>
   <si>
-    <t>MacOS Printer</t>
-  </si>
-  <si>
     <t>An app to print images and text fra a Mac to a PeriPage A6 bluetooth printer</t>
   </si>
   <si>
@@ -779,6 +776,9 @@
   </si>
   <si>
     <t>GitHub|https://github.com/general-ackbar/chr2img</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MacOS utility for PeriPage A6 </t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1281,7 @@
         <v>36</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -1359,7 +1359,7 @@
         <v>52</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>12</v>
@@ -1385,7 +1385,7 @@
         <v>58</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>12</v>
@@ -1411,7 +1411,7 @@
         <v>64</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>12</v>
@@ -1437,7 +1437,7 @@
         <v>70</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>12</v>
@@ -1489,7 +1489,7 @@
         <v>82</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>12</v>
@@ -1747,7 +1747,7 @@
         <v>121</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>30</v>
@@ -1773,7 +1773,7 @@
         <v>121</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>30</v>
@@ -1851,7 +1851,7 @@
         <v>121</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>12</v>
@@ -1929,7 +1929,7 @@
         <v>121</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
@@ -1981,19 +1981,19 @@
         <v>121</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>173</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2007,7 +2007,7 @@
         <v>121</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>12</v>
@@ -2017,7 +2017,7 @@
         <v>175</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2031,7 +2031,7 @@
         <v>230</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>12</v>
@@ -2057,7 +2057,7 @@
         <v>230</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>12</v>
@@ -2083,7 +2083,7 @@
         <v>230</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
@@ -2109,7 +2109,7 @@
         <v>230</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>12</v>
@@ -2287,7 +2287,7 @@
         <v>121</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>12</v>
@@ -2330,7 +2330,7 @@
         <v>242</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>121</v>
@@ -2342,10 +2342,10 @@
         <v>12</v>
       </c>
       <c r="F47" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>241</v>
